--- a/docs/testing/BVA/Table_Point/Table/BVA_Table_TestCase.xlsx
+++ b/docs/testing/BVA/Table_Point/Table/BVA_Table_TestCase.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27726"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uteduvn-my.sharepoint.com/personal/huyna1707_ut_edu_vn/Documents/Backup/Desktop/Clone CNPM/13 thang 9/KCPM-2026/docs/testing/BVA/Table_Point/Table/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="5" documentId="11_FA848B7651AD4D83B9839DE38B856B538997D6EB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4843A688-8A51-46A6-9F4A-DD130BD00802}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="11588"/>
+    <workbookView xWindow="22932" yWindow="996" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BVA_Table_TestCases" sheetId="1" r:id="rId1"/>
@@ -23,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="103">
   <si>
     <t>Test Case ID*</t>
   </si>
@@ -111,9 +112,6 @@
     <t>HTTP 400 Bad Request (7ms). Response: "Bàn #1 đã tồn tại trong hệ thống!".</t>
   </si>
   <si>
-    <t>Fail</t>
-  </si>
-  <si>
     <t>BVA-TB-003</t>
   </si>
   <si>
@@ -370,9 +368,6 @@
 qrCode phải thực sự có độ dài 254 ký tự và response phải echo đúng chuỗi 254 ký tự.</t>
   </si>
   <si>
-    <t>HTTP 201 Created (18ms), nhưng request/response hiển thị literal "{{qr_254}}" thay vì chuỗi 254 ký tự. Chưa thực sự kiểm thử boundary 254 ký tự.</t>
-  </si>
-  <si>
     <t>BVA-TB-013</t>
   </si>
   <si>
@@ -399,9 +394,6 @@
 qrCode phải thực sự có độ dài 255 ký tự và response phải echo đúng chuỗi 255 ký tự.</t>
   </si>
   <si>
-    <t>HTTP 201 Created (12ms), nhưng request/response hiển thị literal "{{qr_255}}" thay vì chuỗi 255 ký tự. Chưa thực sự kiểm thử boundary 255 ký tự.</t>
-  </si>
-  <si>
     <t>FutureSuShi – BVA Table Execution Summary</t>
   </si>
   <si>
@@ -436,12 +428,18 @@
   </si>
   <si>
     <t>BVA-TB-002, BVA-TB-003: tableNumber 1/2 already existed; BVA-TB-012, BVA-TB-013: qr_254/qr_255 variables were sent literally.</t>
+  </si>
+  <si>
+    <t>HTTP 201 Created. Request sử dụng biến {{qr_254}} đã được resolve thành chuỗi 254 ký tự. Response trả về đúng qrCode có độ dài 254 ký tự. Boundary Max-1 hoạt động đúng.</t>
+  </si>
+  <si>
+    <t>HTTP 201 Created. Request sử dụng biến {{qr_255}} đã được resolve thành chuỗi 255 ký tự. Response trả về đúng qrCode có độ dài 255 ký tự. Boundary Max hoạt động đúng.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -452,24 +450,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
       <sz val="14"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
@@ -477,12 +457,32 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="6" tint="-0.249977111117893"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -497,12 +497,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -534,22 +528,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -856,9 +847,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H14"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="2" width="42" customWidth="1"/>
@@ -869,445 +860,445 @@
     <col min="8" max="8" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="32" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:8" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="105" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:8" ht="105" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="H2" s="5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="105" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:8" ht="105" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="6" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="105" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="2" t="s">
+    <row r="4" spans="1:8" ht="105" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="G4" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="H4" s="6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="105" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="B5" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="H5" s="5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="105" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A5" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E5" s="2" t="s">
+    <row r="6" spans="1:8" ht="105" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="F6" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="H5" s="6" t="s">
+      <c r="G6" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="H6" s="5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="105" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A6" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="G6" s="2" t="s">
+    <row r="7" spans="1:8" ht="105" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="H6" s="6" t="s">
+      <c r="B7" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="H7" s="5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="105" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A7" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B7" s="2" t="s">
+    <row r="8" spans="1:8" ht="105" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C8" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="H7" s="6" t="s">
+      <c r="D8" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="H8" s="5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="105" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A8" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="G8" s="2" t="s">
+    <row r="9" spans="1:8" ht="105" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="H8" s="6" t="s">
+      <c r="B9" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="H9" s="5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="105" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="G9" s="2" t="s">
+    <row r="10" spans="1:8" ht="105" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="H9" s="6" t="s">
+      <c r="B10" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="H10" s="5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="105" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A10" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="G10" s="2" t="s">
+    <row r="11" spans="1:8" ht="105" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="H10" s="6" t="s">
+      <c r="B11" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="H11" s="5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="105" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A11" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G11" s="2" t="s">
+    <row r="12" spans="1:8" ht="105" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="H11" s="6" t="s">
+      <c r="B12" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="H12" s="5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="105" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A12" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G12" s="2" t="s">
+    <row r="13" spans="1:8" ht="105" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="H12" s="6" t="s">
+      <c r="B13" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="H13" s="5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="105" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A13" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="F13" s="2" t="s">
+    <row r="14" spans="1:8" ht="105" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="G13" s="2" t="s">
+      <c r="B14" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="H13" s="5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="105" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="2" t="s">
+      <c r="C14" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="D14" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="E14" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="F14" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="E14" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>91</v>
+      <c r="G14" s="4" t="s">
+        <v>102</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H14"/>
+  <autoFilter ref="A1:H14" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="110" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:2" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A2" s="4" t="s">
+      <c r="B3" t="s">
         <v>93</v>
       </c>
-      <c r="B2" s="4" t="s">
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>94</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
-        <v>95</v>
-      </c>
-      <c r="B3" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
-        <v>97</v>
       </c>
       <c r="B4">
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B5">
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B6">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>97</v>
+      </c>
+      <c r="B7" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>99</v>
+      </c>
+      <c r="B8" t="s">
         <v>100</v>
-      </c>
-      <c r="B7" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
-        <v>102</v>
-      </c>
-      <c r="B8" t="s">
-        <v>103</v>
       </c>
     </row>
   </sheetData>
